--- a/exports/trend_1d/PREMIERENE_full_report.xlsx
+++ b/exports/trend_1d/PREMIERENE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>31.58</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45589</v>
+        <v>45590</v>
       </c>
       <c r="H2" t="n">
-        <v>978.35</v>
+        <v>945.05</v>
       </c>
       <c r="I2" t="n">
         <v>957.558032846182</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K2" t="n">
-        <v>-12.12</v>
+        <v>-15.11</v>
       </c>
       <c r="L2" t="n">
-        <v>12.6</v>
+        <v>16.9</v>
       </c>
       <c r="M2" t="n">
         <v>2.29</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>20.66</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="H3" t="n">
-        <v>1075.65</v>
+        <v>1168.15</v>
       </c>
       <c r="I3" t="n">
         <v>1126.546930285752</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>-13.82</v>
+        <v>-23.61</v>
       </c>
       <c r="L3" t="n">
-        <v>18.48</v>
+        <v>25.39</v>
       </c>
       <c r="M3" t="n">
         <v>2.55</v>
       </c>
       <c r="N3" t="n">
-        <v>5.36</v>
+        <v>8.6</v>
       </c>
       <c r="O3" t="n">
         <v>-3.4</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>20.64</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45608</v>
+        <v>45609</v>
       </c>
       <c r="H4" t="n">
-        <v>1028.65</v>
+        <v>982.7</v>
       </c>
       <c r="I4" t="n">
         <v>1007.91258942201</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>-11.94</v>
+        <v>-15.88</v>
       </c>
       <c r="L4" t="n">
-        <v>14.31</v>
+        <v>16.53</v>
       </c>
       <c r="M4" t="n">
         <v>2.48</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>25.56</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45624</v>
+        <v>45625</v>
       </c>
       <c r="H5" t="n">
-        <v>1137.45</v>
+        <v>1222.95</v>
       </c>
       <c r="I5" t="n">
         <v>1198.045659264978</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>-15.75</v>
+        <v>-24.45</v>
       </c>
       <c r="L5" t="n">
-        <v>18.94</v>
+        <v>26.39</v>
       </c>
       <c r="M5" t="n">
         <v>3.02</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>21.05</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="H6" t="n">
-        <v>1212</v>
+        <v>1127.1</v>
       </c>
       <c r="I6" t="n">
         <v>1173.03284487989</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9</v>
+        <v>-7.84</v>
       </c>
       <c r="L6" t="n">
-        <v>8.01</v>
+        <v>8.75</v>
       </c>
       <c r="M6" t="n">
         <v>2.44</v>
       </c>
       <c r="N6" t="n">
-        <v>3.79</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
         <v>7.52</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>20.13</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="H7" t="n">
-        <v>940.75</v>
+        <v>967.25</v>
       </c>
       <c r="I7" t="n">
         <v>956.5996857078724</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K7" t="n">
-        <v>16.53</v>
+        <v>14.18</v>
       </c>
       <c r="L7" t="n">
         <v>7.53</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>14.13</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H8" t="n">
-        <v>1000.3</v>
+        <v>968</v>
       </c>
       <c r="I8" t="n">
         <v>981.1272035866571</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K8" t="n">
-        <v>3.42</v>
+        <v>0.08</v>
       </c>
       <c r="L8" t="n">
         <v>5.19</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>13.99</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="H9" t="n">
-        <v>1074.1</v>
+        <v>1115.8</v>
       </c>
       <c r="I9" t="n">
         <v>1103.463901623833</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>-10.96</v>
+        <v>-15.27</v>
       </c>
       <c r="L9" t="n">
-        <v>13.02</v>
+        <v>15.59</v>
       </c>
       <c r="M9" t="n">
         <v>1.71</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>10.58</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45873</v>
+        <v>45874</v>
       </c>
       <c r="H10" t="n">
-        <v>1019.3</v>
+        <v>997.3</v>
       </c>
       <c r="I10" t="n">
         <v>1006.283969294137</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>-8.65</v>
+        <v>-10.62</v>
       </c>
       <c r="L10" t="n">
-        <v>9.93</v>
+        <v>10.83</v>
       </c>
       <c r="M10" t="n">
         <v>1.98</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>12.84</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="H11" t="n">
-        <v>1070.7</v>
+        <v>1100</v>
       </c>
       <c r="I11" t="n">
         <v>1082.427002270694</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K11" t="n">
-        <v>-7.36</v>
+        <v>-10.3</v>
       </c>
       <c r="L11" t="n">
-        <v>9.6</v>
+        <v>12.21</v>
       </c>
       <c r="M11" t="n">
         <v>1.61</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>8.4</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="H12" t="n">
-        <v>1041.8</v>
+        <v>1004.2</v>
       </c>
       <c r="I12" t="n">
         <v>1009.946558745178</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.29</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>5.91</v>
+        <v>9.09</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>3.61</v>
       </c>
       <c r="O12" t="n">
         <v>2.74</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>11.39</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="H13" t="n">
-        <v>806.4</v>
+        <v>823.85</v>
       </c>
       <c r="I13" t="n">
         <v>807.2760940951206</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K13" t="n">
-        <v>19.7</v>
+        <v>17.96</v>
       </c>
       <c r="L13" t="n">
         <v>6.8</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>13.06</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H14" t="n">
-        <v>731</v>
+        <v>712.85</v>
       </c>
       <c r="I14" t="n">
         <v>716.2787772120544</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>-11.27</v>
+        <v>-13.47</v>
       </c>
       <c r="L14" t="n">
         <v>19.05</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>13.62</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="H15" t="n">
-        <v>795.75</v>
+        <v>811.2</v>
       </c>
       <c r="I15" t="n">
         <v>797.5647329658339</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K15" t="n">
-        <v>-11.63</v>
+        <v>-13.8</v>
       </c>
       <c r="L15" t="n">
-        <v>12.79</v>
+        <v>16.56</v>
       </c>
       <c r="M15" t="n">
         <v>0.96</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>11.79</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="H16" t="n">
-        <v>1036.2</v>
+        <v>982.7</v>
       </c>
       <c r="I16" t="n">
         <v>1010.303144115456</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K16" t="n">
-        <v>27.74</v>
+        <v>21.14</v>
       </c>
       <c r="L16" t="n">
         <v>2.34</v>
@@ -1353,7 +1544,7 @@
         <v>2.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.69</v>
+        <v>5.16</v>
       </c>
       <c r="O16" t="n">
         <v>1.94</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1413,6 +1616,14 @@
       <c r="Q17" t="n">
         <v>62</v>
       </c>
+      <c r="R17" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2427,7 +2638,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44.1</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="6">
@@ -2437,7 +2648,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -2447,7 +2658,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8">
@@ -2457,7 +2668,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -2467,7 +2678,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -2477,7 +2688,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>95.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2517,7 +2728,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-2.82</v>
+        <v>-7.05</v>
       </c>
     </row>
     <row r="15">
@@ -2527,7 +2738,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-2.38</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2748,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-3.33</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="17">
@@ -2547,7 +2758,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27.74</v>
+        <v>24.45</v>
       </c>
     </row>
     <row r="18">
@@ -2567,7 +2778,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10.97</v>
+        <v>13.28</v>
       </c>
     </row>
     <row r="20">
@@ -2577,7 +2788,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.93</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="21">
@@ -2587,7 +2798,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.05</v>
+        <v>26.39</v>
       </c>
     </row>
     <row r="22">
@@ -2607,7 +2818,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -2637,7 +2848,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="27">
@@ -2657,7 +2868,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
